--- a/AAII_Financials/Yearly/SVNDY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SVNDY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="92">
   <si>
     <t>SVNDY</t>
   </si>
@@ -656,149 +656,161 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46081</v>
+      </c>
+      <c r="E7" s="2">
         <v>45716</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45351</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44985</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44620</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44255</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43890</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43524</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43159</v>
       </c>
-      <c r="L7" s="2"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M7" s="2"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>66832900</v>
+      </c>
+      <c r="E8" s="3">
         <v>79660200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>76558500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>86769300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>75904000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>54070400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>61331600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>60973400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>56576200</v>
       </c>
-      <c r="L8" s="3"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M8" s="3"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>46776900</v>
+      </c>
+      <c r="E9" s="3">
         <v>56460100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>53795800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>62470100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>52200600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>32629700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>39134000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>39610500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>35356300</v>
       </c>
-      <c r="L9" s="3"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M9" s="3"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>20056000</v>
+      </c>
+      <c r="E10" s="3">
         <v>23200000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>22762700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>24299200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>23703400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>21440700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>22197600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>21362900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>21220000</v>
       </c>
-      <c r="L10" s="3"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10" s="3"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -811,8 +823,9 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -840,9 +853,12 @@
       <c r="K12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L12" s="3"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="3"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -870,69 +886,78 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-      <c r="L13" s="3"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-380400</v>
+      </c>
+      <c r="E14" s="3">
         <v>649400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1534500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>523100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>405300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>924400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>659100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>800100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1024600</v>
       </c>
-      <c r="L14" s="3"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M14" s="3"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>2376700</v>
+      </c>
+      <c r="E15" s="3">
         <v>2808000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>2589600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>2670800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>2421000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2066900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1978600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1887100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2153200</v>
       </c>
-      <c r="L15" s="3"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M15" s="3"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -942,68 +967,75 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>64122500</v>
+      </c>
+      <c r="E17" s="3">
         <v>76859100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>72993100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>83048300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>72541100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>50635600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>57415400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>57277900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>52906300</v>
       </c>
-      <c r="L17" s="3"/>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M17" s="3"/>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2710400</v>
+      </c>
+      <c r="E18" s="3">
         <v>2801000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3565400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>3721100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>3362900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>3434800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>3916200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>3695400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3670000</v>
       </c>
-      <c r="L18" s="3"/>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M18" s="3"/>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1016,158 +1048,174 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>72500</v>
+      </c>
+      <c r="E20" s="3">
         <v>32600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-13900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>25600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>35100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>22400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>5800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-8300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>39000</v>
       </c>
-      <c r="L20" s="3"/>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M20" s="3"/>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>5014600</v>
+      </c>
+      <c r="E21" s="3">
         <v>5576400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>6169000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>6366300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>5748800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>5479300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>5889000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>5590900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>5784200</v>
       </c>
-      <c r="L21" s="3"/>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M21" s="3"/>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>317100</v>
+      </c>
+      <c r="E22" s="3">
         <v>408400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>287800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>267300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>254600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>99200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>97800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>108700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>82700</v>
       </c>
-      <c r="L22" s="3"/>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M22" s="3"/>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2784500</v>
+      </c>
+      <c r="E23" s="3">
         <v>1792100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1848600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2958800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2705300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2426300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>3198100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2849800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2589200</v>
       </c>
-      <c r="L23" s="3"/>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M23" s="3"/>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>868000</v>
+      </c>
+      <c r="E24" s="3">
         <v>574400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>279000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>812400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>768700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>604200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1027000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>936900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>744200</v>
       </c>
-      <c r="L24" s="3"/>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M24" s="3"/>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1195,69 +1243,78 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-      <c r="L25" s="3"/>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3"/>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1916400</v>
+      </c>
+      <c r="E26" s="3">
         <v>1217700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1569700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2146400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1936600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1822200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2171100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1912900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1845000</v>
       </c>
-      <c r="L26" s="3"/>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M26" s="3"/>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1875900</v>
+      </c>
+      <c r="E27" s="3">
         <v>1151500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1499100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2064100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1828500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1680800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2014000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1822600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1697400</v>
       </c>
-      <c r="L27" s="3"/>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M27" s="3"/>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1285,9 +1342,12 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-      <c r="L28" s="3"/>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3"/>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1315,9 +1375,12 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3"/>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3"/>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1345,9 +1408,12 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-      <c r="L30" s="3"/>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3"/>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1375,69 +1441,78 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-      <c r="L31" s="3"/>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3"/>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-72500</v>
+      </c>
+      <c r="E32" s="3">
         <v>-32600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>13900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-25600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-35100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-22400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-5800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>8300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-39000</v>
       </c>
-      <c r="L32" s="3"/>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M32" s="3"/>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1875900</v>
+      </c>
+      <c r="E33" s="3">
         <v>1151500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1499100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2064100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1828500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1680800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2014000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1822600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1697400</v>
       </c>
-      <c r="L33" s="3"/>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M33" s="3"/>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1465,74 +1540,83 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-      <c r="L34" s="3"/>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3"/>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1875900</v>
+      </c>
+      <c r="E35" s="3">
         <v>1151500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1499100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2064100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1828500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1680800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2014000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1822600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1697400</v>
       </c>
-      <c r="L35" s="3"/>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M35" s="3"/>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46081</v>
+      </c>
+      <c r="E38" s="2">
         <v>45716</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45351</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44985</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44620</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44255</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43890</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43524</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43159</v>
       </c>
-      <c r="L38" s="2"/>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M38" s="2"/>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1545,8 +1629,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1559,38 +1644,42 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2810600</v>
+      </c>
+      <c r="E41" s="3">
         <v>9106300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>10402500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>12274700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>12324100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>20526100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>12532700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>11802500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>12185000</v>
       </c>
-      <c r="L41" s="3"/>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M41" s="3"/>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1618,219 +1707,243 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-      <c r="L42" s="3"/>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3"/>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2139400</v>
+      </c>
+      <c r="E43" s="3">
         <v>3577900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3692600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3884500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3900100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3804900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4133200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3876900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4518600</v>
       </c>
-      <c r="L43" s="3"/>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M43" s="3"/>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1431400</v>
+      </c>
+      <c r="E44" s="3">
         <v>2101100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1907800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2074400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2158500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1512600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1643900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1625200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1658400</v>
       </c>
-      <c r="L44" s="3"/>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M44" s="3"/>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2609700</v>
+      </c>
+      <c r="E45" s="3">
         <v>3372400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3651600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3673500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3595600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>4987600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3965800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3081300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>907300</v>
       </c>
-      <c r="L45" s="3"/>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M45" s="3"/>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>9563600</v>
+      </c>
+      <c r="E46" s="3">
         <v>18787900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>20259000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>22484500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>22596400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>31412700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>22817400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>21126300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>21928500</v>
       </c>
-      <c r="L46" s="3"/>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M46" s="3"/>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>4093300</v>
+      </c>
+      <c r="E47" s="3">
         <v>5187800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>4871000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>5220900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>6091000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>6409400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>6086400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>6011400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1091700</v>
       </c>
-      <c r="L47" s="3"/>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M47" s="3"/>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>28821100</v>
+      </c>
+      <c r="E48" s="3">
         <v>33142800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>29113800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>31895800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>28040600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>20684300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>20153900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>19021600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>18641800</v>
       </c>
-      <c r="L48" s="3"/>
-    </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M48" s="3"/>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>15820500</v>
+      </c>
+      <c r="E49" s="3">
         <v>18040000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>15727000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>17371600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>18564500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>6055900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>5620400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>5463200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4328800</v>
       </c>
-      <c r="L49" s="3"/>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M49" s="3"/>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1858,9 +1971,12 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-      <c r="L50" s="3"/>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3"/>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1888,9 +2004,12 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-      <c r="L51" s="3"/>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3"/>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -1916,11 +2035,14 @@
         <v>0</v>
       </c>
       <c r="K52" s="3">
+        <v>0</v>
+      </c>
+      <c r="L52" s="3">
         <v>5094100</v>
       </c>
-      <c r="L52" s="3"/>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M52" s="3"/>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1948,39 +2070,45 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-      <c r="L53" s="3"/>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3"/>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>58584300</v>
+      </c>
+      <c r="E54" s="3">
         <v>75756900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>70688100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>77510500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>75813100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>65135500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>55355000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>52031800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>51489400</v>
       </c>
-      <c r="L54" s="3"/>
-    </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M54" s="3"/>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1993,8 +2121,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2007,188 +2136,207 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2666100</v>
+      </c>
+      <c r="E57" s="3">
         <v>3456400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3524700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3938900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4197900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3612600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3791900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3695500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5789900</v>
       </c>
-      <c r="L57" s="3"/>
-    </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M57" s="3"/>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4783000</v>
+      </c>
+      <c r="E58" s="3">
         <v>6342400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4870700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>6438800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2788400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>7816200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2749700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2692100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2821100</v>
       </c>
-      <c r="L58" s="3"/>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M58" s="3"/>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3031000</v>
+      </c>
+      <c r="E59" s="3">
         <v>10291100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>10250900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>11466100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>12369100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>13354100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>12022900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>10220400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>8182300</v>
       </c>
-      <c r="L59" s="3"/>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M59" s="3"/>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>12178700</v>
+      </c>
+      <c r="E60" s="3">
         <v>22066900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>20509800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>23986300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>21520200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>26088900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>19912100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>17891900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>18216000</v>
       </c>
-      <c r="L60" s="3"/>
-    </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M60" s="3"/>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>19525900</v>
+      </c>
+      <c r="E61" s="3">
         <v>21594000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>20774800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>23256300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>22358100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>8697400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>6323600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>7230600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>6753000</v>
       </c>
-      <c r="L61" s="3"/>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M61" s="3"/>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1957200</v>
+      </c>
+      <c r="E62" s="3">
         <v>2331100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1787500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2010300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3560400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2967700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2990700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2442900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1961500</v>
       </c>
-      <c r="L62" s="3"/>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M62" s="3"/>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2216,9 +2364,12 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-      <c r="L63" s="3"/>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3"/>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2246,9 +2397,12 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-      <c r="L64" s="3"/>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3"/>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2276,39 +2430,45 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-      <c r="L65" s="3"/>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3"/>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>35208200</v>
+      </c>
+      <c r="E66" s="3">
         <v>47696400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>44656700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>50710000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>48506600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>38588100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>29904200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>28037500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>27357600</v>
       </c>
-      <c r="L66" s="3"/>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M66" s="3"/>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2321,8 +2481,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2350,9 +2511,12 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-      <c r="L68" s="3"/>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3"/>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2380,9 +2544,12 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-      <c r="L69" s="3"/>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3"/>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2410,9 +2577,12 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-      <c r="L70" s="3"/>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3"/>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2440,39 +2610,45 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-      <c r="L71" s="3"/>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3"/>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>18622200</v>
+      </c>
+      <c r="E72" s="3">
         <v>18111800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>17689000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>18604400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>20118600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>20616600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>19448200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>18096900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>17751500</v>
       </c>
-      <c r="L72" s="3"/>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M72" s="3"/>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2500,9 +2676,12 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-      <c r="L73" s="3"/>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3"/>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2530,9 +2709,12 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-      <c r="L74" s="3"/>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3"/>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2560,39 +2742,45 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-      <c r="L75" s="3"/>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3"/>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>23198400</v>
+      </c>
+      <c r="E76" s="3">
         <v>26815300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>24803200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>25525400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>25860200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>25025100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>24017400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>22663000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>22768800</v>
       </c>
-      <c r="L76" s="3"/>
-    </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M76" s="3"/>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2620,74 +2808,83 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-      <c r="L77" s="3"/>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3"/>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46081</v>
+      </c>
+      <c r="E80" s="2">
         <v>45716</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45351</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44985</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44620</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44255</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43890</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43524</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43159</v>
       </c>
-      <c r="L80" s="2"/>
-    </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M80" s="2"/>
+    </row>
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1875900</v>
+      </c>
+      <c r="E81" s="3">
         <v>1151500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1499100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2064100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1828500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1680800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2014000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1822600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1697400</v>
       </c>
-      <c r="L81" s="3"/>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M81" s="3"/>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2700,38 +2897,42 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2447800</v>
+      </c>
+      <c r="E83" s="3">
         <v>2904800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2674700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2762900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2538000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2208200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2090500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1985400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1997400</v>
       </c>
-      <c r="L83" s="3"/>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M83" s="3"/>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2759,9 +2960,12 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-      <c r="L84" s="3"/>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3"/>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2789,9 +2993,12 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-      <c r="L85" s="3"/>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3"/>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2819,9 +3026,12 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-      <c r="L86" s="3"/>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3"/>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2849,9 +3059,12 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-      <c r="L87" s="3"/>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3"/>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2879,39 +3092,45 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-      <c r="L88" s="3"/>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3"/>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4272200</v>
+      </c>
+      <c r="E89" s="3">
         <v>5831500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4491500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>6820900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>6388900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>5063100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>5323000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>5189300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>4669300</v>
       </c>
-      <c r="L89" s="3"/>
-    </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M89" s="3"/>
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2924,38 +3143,42 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2137700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2866700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2252000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2242200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2927900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2792800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2747900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4295700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2604100</v>
       </c>
-      <c r="L91" s="3"/>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M91" s="3"/>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2983,9 +3206,12 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-      <c r="L92" s="3"/>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3"/>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3013,39 +3239,45 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-      <c r="L93" s="3"/>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3"/>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3058600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4872700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2881700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3035700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-21735700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3695400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2935800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-5065200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2252800</v>
       </c>
-      <c r="L94" s="3"/>
-    </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M94" s="3"/>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3058,38 +3290,42 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>727700</v>
+      </c>
+      <c r="E96" s="3">
         <v>674700</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>708000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>659400</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>759000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>816500</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>775200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>734300</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>745500</v>
       </c>
-      <c r="L96" s="3"/>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M96" s="3"/>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3117,9 +3353,12 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-      <c r="L97" s="3"/>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3"/>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3147,9 +3386,12 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-      <c r="L98" s="3"/>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3"/>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3177,97 +3419,109 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-      <c r="L99" s="3"/>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3"/>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-7111700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2612500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2516400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1986200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>8129100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>6474700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1968000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-47800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1579000</v>
       </c>
-      <c r="L100" s="3"/>
-    </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M100" s="3"/>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-20400</v>
+      </c>
+      <c r="E101" s="3">
         <v>238700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>157300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>110400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>547100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-69700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-11900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-47200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>14100</v>
       </c>
-      <c r="L101" s="3"/>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M101" s="3"/>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-5918500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1415000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-749400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1909300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-6670600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>7772800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>407300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>29100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>851600</v>
       </c>
-      <c r="L102" s="3"/>
+      <c r="M102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
